--- a/bigtree/samples/charts/report_charts.xlsx
+++ b/bigtree/samples/charts/report_charts.xlsx
@@ -11,6 +11,8 @@
     <sheet name="graph2" sheetId="4" r:id="rId4"/>
     <sheet name="data3" sheetId="5" r:id="rId5"/>
     <sheet name="graph3" sheetId="6" r:id="rId6"/>
+    <sheet name="data4" sheetId="7" r:id="rId7"/>
+    <sheet name="graph4" sheetId="8" r:id="rId8"/>
   </sheets>
 </workbook>
 </file>
@@ -993,6 +995,312 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="ja-JP"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="percentStacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>data4!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>検索</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:cat>
+            <c:strRef>
+              <c:f>data4!$A$2:$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2026/09</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>data4!$B$2:$B$2</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.58</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>data4!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>SNS</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:cat>
+            <c:strRef>
+              <c:f>data4!$A$2:$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2026/09</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>data4!$C$2:$C$2</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.21</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>data4!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>note 内</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:cat>
+            <c:strRef>
+              <c:f>data4!$A$2:$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2026/09</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>data4!$D$2:$D$2</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.13</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>data4!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>その他</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:cat>
+            <c:strRef>
+              <c:f>data4!$A$2:$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2026/09</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>data4!$E$2:$E$2</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.08</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="60"/>
+        <c:overlap val="100"/>
+        <c:axId val="1001"/>
+        <c:axId val="1002"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9525">
+            <a:solidFill>
+              <a:schemeClr val="tx2"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000">
+                <a:solidFill>
+                  <a:schemeClr val="tx2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1002"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="6350">
+              <a:solidFill>
+                <a:schemeClr val="bg2">
+                  <a:lumMod val="90000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0%" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000">
+                <a:solidFill>
+                  <a:schemeClr val="tx2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1000">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ja-JP"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1000">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:latin typeface="+mn-lt"/>
+          <a:ea typeface="+mn-ea"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="ja-JP"/>
+    </a:p>
+  </c:txPr>
+</c:chartSpace>
+</file>
+
 <file path=xl/chartsheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <drawing r:id="rId1"/>
@@ -1006,6 +1314,12 @@
 </file>
 
 <file path=xl/chartsheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <drawing r:id="rId1"/>
+</chartsheet>
+</file>
+
+<file path=xl/chartsheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <drawing r:id="rId1"/>
 </chartsheet>
@@ -1073,6 +1387,33 @@
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="graph3"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks noGrp="1"/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="0" y="0"/>
+    <xdr:ext cx="8670000" cy="6300000"/>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="graph4"/>
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks noGrp="1"/>
         </xdr:cNvGraphicFramePr>
@@ -1458,4 +1799,55 @@
     </row>
   </sheetData>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="4" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr" s="3">
+        <is>
+          <t>検索</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr" s="3">
+        <is>
+          <t>SNS</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr" s="3">
+        <is>
+          <t>note 内</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr" s="3">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026/09</t>
+        </is>
+      </c>
+      <c r="B2" s="2">
+        <v>0.58</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0.21</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0.13</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0.08</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>
--- a/bigtree/samples/charts/report_charts.xlsx
+++ b/bigtree/samples/charts/report_charts.xlsx
@@ -13,6 +13,8 @@
     <sheet name="graph3" sheetId="6" r:id="rId6"/>
     <sheet name="data4" sheetId="7" r:id="rId7"/>
     <sheet name="graph4" sheetId="8" r:id="rId8"/>
+    <sheet name="data5" sheetId="9" r:id="rId9"/>
+    <sheet name="graph5" sheetId="10" r:id="rId10"/>
   </sheets>
 </workbook>
 </file>
@@ -95,6 +97,31 @@
               </c:strCache>
             </c:strRef>
           </c:tx>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1100">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>data1!$A$2:$A$5</c:f>
@@ -151,6 +178,31 @@
               </c:strCache>
             </c:strRef>
           </c:tx>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1100">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>data1!$A$2:$A$5</c:f>
@@ -221,7 +273,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000">
+              <a:defRPr sz="1100">
                 <a:solidFill>
                   <a:schemeClr val="tx2"/>
                 </a:solidFill>
@@ -242,16 +294,15 @@
         <c:axId val="1002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:min val="0"/>
         </c:scaling>
-        <c:delete val="0"/>
+        <c:delete val="1"/>
         <c:axPos val="l"/>
         <c:majorGridlines>
           <c:spPr>
             <a:ln w="6350">
               <a:solidFill>
-                <a:schemeClr val="bg2">
-                  <a:lumMod val="90000"/>
-                </a:schemeClr>
+                <a:schemeClr val="accent5"/>
               </a:solidFill>
             </a:ln>
           </c:spPr>
@@ -270,7 +321,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000">
+              <a:defRPr sz="1100">
                 <a:solidFill>
                   <a:schemeClr val="tx2"/>
                 </a:solidFill>
@@ -294,7 +345,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1000">
+            <a:defRPr sz="1100">
               <a:solidFill>
                 <a:schemeClr val="tx1"/>
               </a:solidFill>
@@ -320,7 +371,7 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr sz="1000">
+        <a:defRPr sz="1100">
           <a:solidFill>
             <a:schemeClr val="tx1"/>
           </a:solidFill>
@@ -363,14 +414,49 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="tx2"/>
+                <a:schemeClr val="accent4"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
           </c:spPr>
           <c:marker>
-            <c:symbol val="none"/>
+            <c:symbol val="circle"/>
+            <c:size val="6"/>
           </c:marker>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:txPr>
+                <a:bodyPr/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1100">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="1"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>data2!$A$2:$A$5</c:f>
@@ -431,14 +517,49 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="tx2"/>
+                <a:schemeClr val="accent4"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
           </c:spPr>
           <c:marker>
-            <c:symbol val="none"/>
+            <c:symbol val="circle"/>
+            <c:size val="6"/>
           </c:marker>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:txPr>
+                <a:bodyPr/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1100">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="1"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>data2!$A$2:$A$5</c:f>
@@ -505,8 +626,69 @@
             </a:ln>
           </c:spPr>
           <c:marker>
-            <c:symbol val="none"/>
+            <c:symbol val="circle"/>
+            <c:size val="6"/>
           </c:marker>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:txPr>
+                <a:bodyPr/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1100">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:txPr>
+                <a:bodyPr/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1100">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="1"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>data2!$A$2:$A$5</c:f>
@@ -577,7 +759,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000">
+              <a:defRPr sz="1100">
                 <a:solidFill>
                   <a:schemeClr val="tx2"/>
                 </a:solidFill>
@@ -605,9 +787,7 @@
           <c:spPr>
             <a:ln w="6350">
               <a:solidFill>
-                <a:schemeClr val="bg2">
-                  <a:lumMod val="90000"/>
-                </a:schemeClr>
+                <a:schemeClr val="accent5"/>
               </a:solidFill>
             </a:ln>
           </c:spPr>
@@ -626,7 +806,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000">
+              <a:defRPr sz="1100">
                 <a:solidFill>
                   <a:schemeClr val="tx2"/>
                 </a:solidFill>
@@ -642,26 +822,6 @@
         <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
-      <c:txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1000">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="ja-JP"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
   </c:chart>
@@ -676,7 +836,7 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr sz="1000">
+        <a:defRPr sz="1100">
           <a:solidFill>
             <a:schemeClr val="tx1"/>
           </a:solidFill>
@@ -744,6 +904,31 @@
               </a:ln>
             </c:spPr>
           </c:dPt>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1100">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>data3!$A$2:$A$5</c:f>
@@ -812,6 +997,31 @@
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1100">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>data3!$A$2:$A$5</c:f>
@@ -882,7 +1092,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000">
+              <a:defRPr sz="1100">
                 <a:solidFill>
                   <a:schemeClr val="tx2"/>
                 </a:solidFill>
@@ -903,16 +1113,15 @@
         <c:axId val="1002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:min val="0"/>
         </c:scaling>
-        <c:delete val="0"/>
+        <c:delete val="1"/>
         <c:axPos val="l"/>
         <c:majorGridlines>
           <c:spPr>
             <a:ln w="6350">
               <a:solidFill>
-                <a:schemeClr val="bg2">
-                  <a:lumMod val="90000"/>
-                </a:schemeClr>
+                <a:schemeClr val="accent5"/>
               </a:solidFill>
             </a:ln>
           </c:spPr>
@@ -931,7 +1140,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000">
+              <a:defRPr sz="1100">
                 <a:solidFill>
                   <a:schemeClr val="tx2"/>
                 </a:solidFill>
@@ -955,7 +1164,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1000">
+            <a:defRPr sz="1100">
               <a:solidFill>
                 <a:schemeClr val="tx1"/>
               </a:solidFill>
@@ -981,7 +1190,7 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr sz="1000">
+        <a:defRPr sz="1100">
           <a:solidFill>
             <a:schemeClr val="tx1"/>
           </a:solidFill>
@@ -1022,6 +1231,31 @@
               </c:strCache>
             </c:strRef>
           </c:tx>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1100">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>data4!$A$2:$A$2</c:f>
@@ -1060,6 +1294,31 @@
               </c:strCache>
             </c:strRef>
           </c:tx>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1100">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>data4!$A$2:$A$2</c:f>
@@ -1098,6 +1357,31 @@
               </c:strCache>
             </c:strRef>
           </c:tx>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1100">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>data4!$A$2:$A$2</c:f>
@@ -1136,6 +1420,31 @@
               </c:strCache>
             </c:strRef>
           </c:tx>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1100">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>data4!$A$2:$A$2</c:f>
@@ -1170,7 +1479,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="1"/>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
@@ -1188,7 +1497,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000">
+              <a:defRPr sz="1100">
                 <a:solidFill>
                   <a:schemeClr val="tx2"/>
                 </a:solidFill>
@@ -1210,15 +1519,13 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="0"/>
+        <c:delete val="1"/>
         <c:axPos val="b"/>
         <c:majorGridlines>
           <c:spPr>
             <a:ln w="6350">
               <a:solidFill>
-                <a:schemeClr val="bg2">
-                  <a:lumMod val="90000"/>
-                </a:schemeClr>
+                <a:schemeClr val="accent5"/>
               </a:solidFill>
             </a:ln>
           </c:spPr>
@@ -1237,7 +1544,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000">
+              <a:defRPr sz="1100">
                 <a:solidFill>
                   <a:schemeClr val="tx2"/>
                 </a:solidFill>
@@ -1261,7 +1568,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1000">
+            <a:defRPr sz="1100">
               <a:solidFill>
                 <a:schemeClr val="tx1"/>
               </a:solidFill>
@@ -1287,7 +1594,417 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr sz="1000">
+        <a:defRPr sz="1100">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:latin typeface="+mn-lt"/>
+          <a:ea typeface="+mn-ea"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="ja-JP"/>
+    </a:p>
+  </c:txPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="ja-JP"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>data5!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>セッション（件）</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>data5!$A$2:$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>W35</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>W36</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>W37</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>W38</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>data5!$B$2:$B$5</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>12480</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>13102</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>12955</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>14230</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="80"/>
+        <c:axId val="1001"/>
+        <c:axId val="1002"/>
+      </c:barChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>data5!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>CVR（%）</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="34925" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="6"/>
+          </c:marker>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:txPr>
+                <a:bodyPr/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1100">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:txPr>
+                <a:bodyPr/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1100">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="1"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+            </c:dLbl>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>data5!$A$2:$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>W35</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>W36</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>W37</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>W38</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>data5!$C$2:$C$5</c:f>
+              <c:numCache>
+                <c:formatCode>0.0%</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.021</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.023</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.024</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.022</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:marker val="1"/>
+        <c:axId val="1003"/>
+        <c:axId val="1004"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9525">
+            <a:solidFill>
+              <a:schemeClr val="tx2"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="tx2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1002"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="6350">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="tx2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1004"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="0.0%" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="tx2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1003"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="0.005"/>
+      </c:valAx>
+      <c:catAx>
+        <c:axId val="1003"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9525">
+            <a:solidFill>
+              <a:schemeClr val="tx2"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="tx2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1004"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1100">
           <a:solidFill>
             <a:schemeClr val="tx1"/>
           </a:solidFill>
@@ -1320,6 +2037,12 @@
 </file>
 
 <file path=xl/chartsheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <drawing r:id="rId1"/>
+</chartsheet>
+</file>
+
+<file path=xl/chartsheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <drawing r:id="rId1"/>
 </chartsheet>
@@ -1414,6 +2137,33 @@
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="graph4"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks noGrp="1"/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="0" y="0"/>
+    <xdr:ext cx="8670000" cy="6300000"/>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="graph5"/>
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks noGrp="1"/>
         </xdr:cNvGraphicFramePr>
@@ -1850,4 +2600,78 @@
     </row>
   </sheetData>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="4" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr" s="3">
+        <is>
+          <t>セッション（件）</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr" s="3">
+        <is>
+          <t>CVR（%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>W35</t>
+        </is>
+      </c>
+      <c r="B2" s="1">
+        <v>12480</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0.021</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>W36</t>
+        </is>
+      </c>
+      <c r="B3" s="1">
+        <v>13102</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.023</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>W37</t>
+        </is>
+      </c>
+      <c r="B4" s="1">
+        <v>12955</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.024</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>W38</t>
+        </is>
+      </c>
+      <c r="B5" s="1">
+        <v>14230</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0.022</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>
--- a/bigtree/samples/charts/report_charts.xlsx
+++ b/bigtree/samples/charts/report_charts.xlsx
@@ -15,6 +15,12 @@
     <sheet name="graph4" sheetId="8" r:id="rId8"/>
     <sheet name="data5" sheetId="9" r:id="rId9"/>
     <sheet name="graph5" sheetId="10" r:id="rId10"/>
+    <sheet name="data7" sheetId="11" r:id="rId11"/>
+    <sheet name="graph7" sheetId="12" r:id="rId12"/>
+    <sheet name="data8" sheetId="13" r:id="rId13"/>
+    <sheet name="graph8" sheetId="14" r:id="rId14"/>
+    <sheet name="data6" sheetId="15" r:id="rId15"/>
+    <sheet name="graph6" sheetId="16" r:id="rId16"/>
   </sheets>
 </workbook>
 </file>
@@ -1239,7 +1245,7 @@
                 <a:pPr>
                   <a:defRPr sz="1100">
                     <a:solidFill>
-                      <a:schemeClr val="tx1"/>
+                      <a:schemeClr val="lt1"/>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
                     <a:ea typeface="+mn-ea"/>
@@ -1365,7 +1371,7 @@
                 <a:pPr>
                   <a:defRPr sz="1100">
                     <a:solidFill>
-                      <a:schemeClr val="tx1"/>
+                      <a:schemeClr val="lt1"/>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
                     <a:ea typeface="+mn-ea"/>
@@ -1518,18 +1524,11 @@
         <c:axId val="1002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="1"/>
+          <c:min val="0"/>
         </c:scaling>
-        <c:delete val="1"/>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="6350">
-              <a:solidFill>
-                <a:schemeClr val="accent5"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-        </c:majorGridlines>
         <c:numFmt formatCode="0%" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -2018,6 +2017,1207 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="ja-JP"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>data7!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>前年</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1100">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>data7!$A$2:$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>検索</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>SNS</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>内部リンク</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>その他</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>data7!$B$2:$B$5</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>2140</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1280</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>640</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>320</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>data7!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>今年</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1100">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>data7!$A$2:$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>検索</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>SNS</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>内部リンク</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>その他</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>data7!$C$2:$C$5</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>3480</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1020</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>980</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>410</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="60"/>
+        <c:overlap val="-10"/>
+        <c:axId val="1001"/>
+        <c:axId val="1002"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1001"/>
+        <c:scaling>
+          <c:orientation val="maxMin"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9525">
+            <a:solidFill>
+              <a:schemeClr val="tx2"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="tx2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1002"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="#,##0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="tx2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1001"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ja-JP"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1100">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:latin typeface="+mn-lt"/>
+          <a:ea typeface="+mn-ea"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="ja-JP"/>
+    </a:p>
+  </c:txPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:strDim type="cat">
+        <cx:f>data8!$A$2:$A$7</cx:f>
+        <cx:lvl ptCount="6">
+          <cx:pt idx="0">8月</cx:pt>
+          <cx:pt idx="1">検索</cx:pt>
+          <cx:pt idx="2">その他</cx:pt>
+          <cx:pt idx="3">内部リンク</cx:pt>
+          <cx:pt idx="4">SNS</cx:pt>
+          <cx:pt idx="5">9月</cx:pt>
+        </cx:lvl>
+      </cx:strDim>
+      <cx:numDim type="val">
+        <cx:f>data8!$B$2:$B$7</cx:f>
+        <cx:lvl ptCount="6" formatCode="#,##0">
+          <cx:pt idx="0">12480</cx:pt>
+          <cx:pt idx="1">1340</cx:pt>
+          <cx:pt idx="2">690</cx:pt>
+          <cx:pt idx="3">340</cx:pt>
+          <cx:pt idx="4">-620</cx:pt>
+          <cx:pt idx="5">14230</cx:pt>
+        </cx:lvl>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="waterfall" uniqueId="{00000000-1111-2222-3333-444444444444}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>data8!$B$1</cx:f>
+              <cx:v>増減</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataLabels pos="outEnd">
+            <cx:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1100">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </cx:txPr>
+            <cx:visibility seriesName="0" categoryName="0" value="1"/>
+          </cx:dataLabels>
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:subtotals>
+              <cx:idx val="0"/>
+              <cx:idx val="5"/>
+            </cx:subtotals>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0">
+        <cx:catScaling gapWidth="0.5"/>
+        <cx:tickLabels/>
+        <cx:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </cx:txPr>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling/>
+        <cx:majorGridlines/>
+        <cx:tickLabels/>
+        <cx:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </cx:txPr>
+      </cx:axis>
+    </cx:plotArea>
+  </cx:chart>
+  <cx:spPr>
+    <a:noFill/>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+  </cx:spPr>
+</cx:chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="ja-JP"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>data6!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>土台</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>data6!$A$2:$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>8月</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>検索</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>その他</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>内部リンク</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>SNS</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9月</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>data6!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>12480</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>13820</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>14510</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>14230</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>data6!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>増加</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1100">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>data6!$A$2:$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>8月</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>検索</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>その他</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>内部リンク</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>SNS</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9月</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>data6!$C$2:$C$7</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="1">
+                  <c:v>1340</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>690</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>340</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>data6!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>減少</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1100">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>data6!$A$2:$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>8月</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>検索</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>その他</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>内部リンク</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>SNS</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9月</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>data6!$D$2:$D$7</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="4">
+                  <c:v>620</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>data6!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>合計</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1100">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>data6!$A$2:$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>8月</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>検索</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>その他</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>内部リンク</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>SNS</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9月</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>data6!$E$2:$E$7</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>12480</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>14230</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="60"/>
+        <c:overlap val="100"/>
+        <c:axId val="1001"/>
+        <c:axId val="1002"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9525">
+            <a:solidFill>
+              <a:schemeClr val="tx2"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="tx2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1002"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="11000"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="6350">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1100">
+                <a:solidFill>
+                  <a:schemeClr val="tx2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1100">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:latin typeface="+mn-lt"/>
+          <a:ea typeface="+mn-ea"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="ja-JP"/>
+    </a:p>
+  </c:txPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="tx1"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent2"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:defRPr/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:defRPr/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:defRPr/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPointMarker>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:defRPr/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:defRPr/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:defRPr/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:defRPr/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:defRPr/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:defRPr/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+</cs:chartStyle>
+</file>
+
 <file path=xl/chartsheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <drawing r:id="rId1"/>
@@ -2043,6 +3243,24 @@
 </file>
 
 <file path=xl/chartsheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <drawing r:id="rId1"/>
+</chartsheet>
+</file>
+
+<file path=xl/chartsheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <drawing r:id="rId1"/>
+</chartsheet>
+</file>
+
+<file path=xl/chartsheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <drawing r:id="rId1"/>
+</chartsheet>
+</file>
+
+<file path=xl/chartsheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <drawing r:id="rId1"/>
 </chartsheet>
@@ -2164,6 +3382,87 @@
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="graph5"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks noGrp="1"/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="0" y="0"/>
+    <xdr:ext cx="8670000" cy="6300000"/>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="graph7"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks noGrp="1"/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="0" y="0"/>
+    <xdr:ext cx="8670000" cy="6300000"/>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="graph8"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks noGrp="1"/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+          <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="0" y="0"/>
+    <xdr:ext cx="8670000" cy="6300000"/>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="graph6"/>
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks noGrp="1"/>
         </xdr:cNvGraphicFramePr>
@@ -2674,4 +3973,265 @@
     </row>
   </sheetData>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="4" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr" s="3">
+        <is>
+          <t>前年</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr" s="3">
+        <is>
+          <t>今年</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>検索</t>
+        </is>
+      </c>
+      <c r="B2" s="1">
+        <v>2140</v>
+      </c>
+      <c r="C2" s="1">
+        <v>3480</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SNS</t>
+        </is>
+      </c>
+      <c r="B3" s="1">
+        <v>1280</v>
+      </c>
+      <c r="C3" s="1">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>内部リンク</t>
+        </is>
+      </c>
+      <c r="B4" s="1">
+        <v>640</v>
+      </c>
+      <c r="C4" s="1">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="B5" s="1">
+        <v>320</v>
+      </c>
+      <c r="C5" s="1">
+        <v>410</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="4" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr" s="3">
+        <is>
+          <t>増減</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>8月</t>
+        </is>
+      </c>
+      <c r="B2" s="1">
+        <v>12480</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>検索</t>
+        </is>
+      </c>
+      <c r="B3" s="1">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="B4" s="1">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>内部リンク</t>
+        </is>
+      </c>
+      <c r="B5" s="1">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SNS</t>
+        </is>
+      </c>
+      <c r="B6" s="1">
+        <v>-620</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>9月</t>
+        </is>
+      </c>
+      <c r="B7" s="1">
+        <v>14230</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="4" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr" s="3">
+        <is>
+          <t>土台</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr" s="3">
+        <is>
+          <t>増加</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr" s="3">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr" s="3">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>8月</t>
+        </is>
+      </c>
+      <c r="B2" s="1">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1">
+        <v>12480</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>検索</t>
+        </is>
+      </c>
+      <c r="B3" s="1">
+        <v>12480</v>
+      </c>
+      <c r="C3" s="1">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="B4" s="1">
+        <v>13820</v>
+      </c>
+      <c r="C4" s="1">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>内部リンク</t>
+        </is>
+      </c>
+      <c r="B5" s="1">
+        <v>14510</v>
+      </c>
+      <c r="C5" s="1">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SNS</t>
+        </is>
+      </c>
+      <c r="B6" s="1">
+        <v>14230</v>
+      </c>
+      <c r="D6" s="1">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>9月</t>
+        </is>
+      </c>
+      <c r="B7" s="1">
+        <v>0</v>
+      </c>
+      <c r="E7" s="1">
+        <v>14230</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>
--- a/bigtree/samples/charts/report_charts.xlsx
+++ b/bigtree/samples/charts/report_charts.xlsx
@@ -3027,6 +3027,13 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
   </cs:dataPointLine>
   <cs:dataPointMarker>
     <cs:lnRef idx="0"/>

--- a/bigtree/samples/charts/report_charts.xlsx
+++ b/bigtree/samples/charts/report_charts.xlsx
@@ -1483,7 +1483,7 @@
       <c:catAx>
         <c:axId val="1001"/>
         <c:scaling>
-          <c:orientation val="minMax"/>
+          <c:orientation val="maxMin"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -1555,7 +1555,7 @@
           </a:p>
         </c:txPr>
         <c:crossAx val="1001"/>
-        <c:crosses val="autoZero"/>
+        <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
